--- a/CookingSystem/docs/arte-e-fluxo.xlsx
+++ b/CookingSystem/docs/arte-e-fluxo.xlsx
@@ -15,10 +15,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Arte necessária'!$A$1:$L$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Já feito em código'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Já feito em código'!$A$1:$E$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Como inserir'!$A$1:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cliques e teclas'!$A$1:$G$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fluxo de telas'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fluxo de telas'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3170,7 +3170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>GameScreen.Dimmer</t>
+          <t>ContextNavigator · GameScreen.Dimmer</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3437,55 +3437,82 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>HUD (barra superior)</t>
+          <t>Fades entre telas e entre cenas</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>GameScreen.RefreshHud</t>
+          <t>ContextNavigator · SceneTransition</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>PanelSkin</t>
+          <t>preto</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Só os ícones (aba Arte)</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>0,12 s no painel, 0,18 s entre cenas.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>HUD (barra superior)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>GameScreen.RefreshHud</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>PanelSkin</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Só os ícones (aba Arte)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Fonte</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>padrão do Godot</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Opcional, futuro</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Para trocar: Projeto › Configurações › GUI › Tema › Fonte personalizada.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4133,12 +4160,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Fecha. Geladeira/loja abertas pelo fogão voltam ao fogão.</t>
+          <t>Volta uma tela (Mercearia › Fogão › casa). O cursor volta ao ladrilho de onde saiu.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>HouseInteractions.Back / Close</t>
+          <t>ContextNavigator.Back</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4345,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Abre o painel manual.</t>
+          <t>Empilha o painel manual sobre o fogão (título “Fogão › Cozinha”).</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4670,7 +4697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4819,34 +4846,34 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>✕ / Esc / B</t>
+          <t>verbo que abre outra tela (ex.: Comprar mantimentos…)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Casa + 2 telas na pilha</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>volta a correr</t>
+          <t>parado</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Casa + painel aberto</t>
+          <t>Casa + 2 telas na pilha</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>trocar de contexto dentro do painel</t>
+          <t>✕ / Esc / B</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Casa + outro painel</t>
+          <t>Casa + painel aberto (a de baixo)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -4858,44 +4885,44 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>Casa + painel aberto</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>✕ / Esc / B na última tela</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>Casa</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Esc / Start / botão Menu</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Pausa</t>
-        </is>
-      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>parado</t>
+          <t>volta a correr</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Esc / Start / botão Menu</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>Pausa</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Continuar / Esc</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Casa</t>
-        </is>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>volta a correr</t>
+          <t>parado</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4934,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Menu principal</t>
+          <t>Continuar / Esc</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Menu principal</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>a casa é descartada (ainda não há save)</t>
+          <t>volta a correr</t>
         </is>
       </c>
     </row>
@@ -4929,22 +4956,44 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>Menu principal</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Menu principal</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>a casa é descartada (ainda não há save)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Pausa</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Sair do jogo</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>(fecha)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter ref="A1:D13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>